--- a/GRM_Data.xlsx
+++ b/GRM_Data.xlsx
@@ -5,15 +5,15 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\testd\Desktop\Hana Contact Mgr\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipTime Cloud\Hana Contact Mgr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADB40CF-62BA-41EE-A7C3-34EC3EECF699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED5F340-5597-4900-BD35-6591E2D18A29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="GRM별_지점코드" sheetId="15" r:id="rId1"/>
+    <sheet name="GRM별_지점코드" sheetId="16" r:id="rId1"/>
     <sheet name="백업1 (2)" sheetId="8" state="hidden" r:id="rId2"/>
   </sheets>
   <definedNames>
@@ -974,34 +974,28 @@
     <t>[직할사업단] - 전혜정/이호준/김민준</t>
   </si>
   <si>
-    <t>[4사업단] - 김정운</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>[2사업단] - 오영주</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>G7247396</t>
-  </si>
-  <si>
-    <t>[2사업단] - 정지혜</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>G7247402</t>
   </si>
   <si>
+    <t>G7247403</t>
+  </si>
+  <si>
+    <t>[2사업단] - 오영주</t>
+  </si>
+  <si>
+    <t>[2사업단] - 정지혜</t>
+  </si>
+  <si>
     <t>[3사업단] - 이선미</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>[3사업단] - 조현주</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>G7247403</t>
-    <phoneticPr fontId="2" type="noConversion"/>
+    <t>[4사업단] - 김정운</t>
   </si>
 </sst>
 </file>
@@ -1893,17 +1887,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{200FDD0B-215F-4AD7-9180-9E2BD6BED19F}">
-  <dimension ref="A1:Y558"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43632162-6062-4115-94E3-85A33C9D95E4}">
+  <dimension ref="A1:Y572"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="6" width="17.75" style="49" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.625" style="49" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.75" style="49" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="20" style="49" bestFit="1" customWidth="1"/>
-    <col min="11" max="14" width="17.75" style="49" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="20" style="49" bestFit="1" customWidth="1"/>
-    <col min="17" max="20" width="17.75" style="49" bestFit="1" customWidth="1"/>
+    <col min="8" max="20" width="17.75" style="49" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15.625" style="49" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="17.75" style="49" bestFit="1" customWidth="1"/>
     <col min="23" max="24" width="21" style="49" bestFit="1" customWidth="1"/>
@@ -1936,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="I1" s="49" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="J1" s="49" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K1" s="49" t="s">
         <v>27</v>
@@ -1957,7 +1947,7 @@
         <v>267</v>
       </c>
       <c r="P1" s="49" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="Q1" s="49" t="s">
         <v>2</v>
@@ -2013,10 +2003,10 @@
         <v>298</v>
       </c>
       <c r="I2" s="49" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J2" s="49" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="K2" s="49" t="s">
         <v>299</v>
@@ -2039,34 +2029,34 @@
       <c r="Q2" s="49" t="s">
         <v>303</v>
       </c>
-      <c r="R2" t="s">
-        <v>311</v>
-      </c>
-      <c r="S2" t="s">
+      <c r="R2" s="49" t="s">
+        <v>318</v>
+      </c>
+      <c r="S2" s="49" t="s">
         <v>304</v>
       </c>
-      <c r="T2" t="s">
+      <c r="T2" s="49" t="s">
         <v>305</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" s="49" t="s">
         <v>306</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" s="49" t="s">
         <v>307</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" s="49" t="s">
         <v>308</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" s="49" t="s">
         <v>309</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Y2" s="49" t="s">
         <v>310</v>
       </c>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3" s="49">
-        <v>988956</v>
+        <v>954055</v>
       </c>
       <c r="B3" s="49">
         <v>988994</v>
@@ -2143,7 +2133,7 @@
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4" s="49">
-        <v>980114</v>
+        <v>954074</v>
       </c>
       <c r="B4" s="49">
         <v>995083</v>
@@ -2220,7 +2210,7 @@
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5" s="49">
-        <v>996401</v>
+        <v>954106</v>
       </c>
       <c r="B5" s="49">
         <v>989088</v>
@@ -2297,7 +2287,7 @@
     </row>
     <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6" s="49">
-        <v>991165</v>
+        <v>954109</v>
       </c>
       <c r="B6" s="49">
         <v>972001</v>
@@ -2374,7 +2364,7 @@
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7" s="49">
-        <v>975145</v>
+        <v>954112</v>
       </c>
       <c r="B7" s="49">
         <v>972075</v>
@@ -2451,7 +2441,7 @@
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8" s="49">
-        <v>986063</v>
+        <v>954134</v>
       </c>
       <c r="B8" s="49">
         <v>978053</v>
@@ -2528,7 +2518,7 @@
     </row>
     <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9" s="49">
-        <v>940063</v>
+        <v>954147</v>
       </c>
       <c r="B9" s="49">
         <v>982005</v>
@@ -2605,7 +2595,7 @@
     </row>
     <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10" s="49">
-        <v>996021</v>
+        <v>954164</v>
       </c>
       <c r="B10" s="49">
         <v>955073</v>
@@ -2682,7 +2672,7 @@
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11" s="49">
-        <v>995325</v>
+        <v>954174</v>
       </c>
       <c r="B11" s="49">
         <v>988952</v>
@@ -2759,7 +2749,7 @@
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12" s="49">
-        <v>955072</v>
+        <v>954208</v>
       </c>
       <c r="B12" s="49">
         <v>972034</v>
@@ -2836,7 +2826,7 @@
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13" s="49">
-        <v>955107</v>
+        <v>954217</v>
       </c>
       <c r="B13" s="49">
         <v>972016</v>
@@ -2913,7 +2903,7 @@
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14" s="49">
-        <v>982010</v>
+        <v>954226</v>
       </c>
       <c r="B14" s="49">
         <v>995248</v>
@@ -2990,7 +2980,7 @@
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15" s="49">
-        <v>993087</v>
+        <v>954232</v>
       </c>
       <c r="B15" s="49">
         <v>979003</v>
@@ -3067,7 +3057,7 @@
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16" s="49">
-        <v>995109</v>
+        <v>954285</v>
       </c>
       <c r="B16" s="49">
         <v>995194</v>
@@ -3144,7 +3134,7 @@
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17" s="49">
-        <v>976077</v>
+        <v>955067</v>
       </c>
       <c r="B17" s="49">
         <v>996039</v>
@@ -3221,7 +3211,7 @@
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18" s="49">
-        <v>992698</v>
+        <v>955072</v>
       </c>
       <c r="B18" s="49">
         <v>996070</v>
@@ -3298,7 +3288,7 @@
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19" s="49">
-        <v>993124</v>
+        <v>955107</v>
       </c>
       <c r="B19" s="49">
         <v>980003</v>
@@ -3375,7 +3365,7 @@
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20" s="49">
-        <v>972018</v>
+        <v>958004</v>
       </c>
       <c r="B20" s="49">
         <v>991112</v>
@@ -3452,7 +3442,7 @@
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A21" s="49">
-        <v>972010</v>
+        <v>958020</v>
       </c>
       <c r="B21" s="49">
         <v>993054</v>
@@ -3529,7 +3519,7 @@
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" s="49">
-        <v>992454</v>
+        <v>959005</v>
       </c>
       <c r="B22" s="49">
         <v>996074</v>
@@ -3606,7 +3596,7 @@
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23" s="49">
-        <v>996023</v>
+        <v>959026</v>
       </c>
       <c r="B23" s="49">
         <v>954115</v>
@@ -3683,7 +3673,7 @@
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24" s="49">
-        <v>988739</v>
+        <v>959044</v>
       </c>
       <c r="B24" s="49">
         <v>995193</v>
@@ -3760,7 +3750,7 @@
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25" s="49">
-        <v>996022</v>
+        <v>960010</v>
       </c>
       <c r="B25" s="49">
         <v>988106</v>
@@ -3837,7 +3827,7 @@
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26" s="49">
-        <v>992059</v>
+        <v>960014</v>
       </c>
       <c r="B26" s="49">
         <v>996386</v>
@@ -3914,7 +3904,7 @@
     </row>
     <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27" s="49">
-        <v>995197</v>
+        <v>960043</v>
       </c>
       <c r="B27" s="49">
         <v>954045</v>
@@ -3991,7 +3981,7 @@
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28" s="49">
-        <v>989216</v>
+        <v>960058</v>
       </c>
       <c r="B28" s="49">
         <v>988093</v>
@@ -4068,7 +4058,7 @@
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29" s="49">
-        <v>996026</v>
+        <v>966040</v>
       </c>
       <c r="B29" s="49">
         <v>983094</v>
@@ -4145,7 +4135,7 @@
     </row>
     <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30" s="49">
-        <v>988013</v>
+        <v>966041</v>
       </c>
       <c r="B30" s="49">
         <v>988097</v>
@@ -4222,7 +4212,7 @@
     </row>
     <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31" s="49">
-        <v>995232</v>
+        <v>966069</v>
       </c>
       <c r="B31" s="49">
         <v>988105</v>
@@ -4299,7 +4289,7 @@
     </row>
     <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32" s="49">
-        <v>988378</v>
+        <v>966214</v>
       </c>
       <c r="B32" s="49">
         <v>995258</v>
@@ -4376,7 +4366,7 @@
     </row>
     <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="49">
-        <v>988048</v>
+        <v>967029</v>
       </c>
       <c r="B33" s="49">
         <v>986119</v>
@@ -4453,7 +4443,7 @@
     </row>
     <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="49">
-        <v>992076</v>
+        <v>967032</v>
       </c>
       <c r="B34" s="49">
         <v>986120</v>
@@ -4530,7 +4520,7 @@
     </row>
     <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="49">
-        <v>996385</v>
+        <v>967033</v>
       </c>
       <c r="B35" s="49">
         <v>996384</v>
@@ -4607,7 +4597,7 @@
     </row>
     <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="49">
-        <v>991010</v>
+        <v>968015</v>
       </c>
       <c r="B36" s="49">
         <v>996044</v>
@@ -4684,7 +4674,7 @@
     </row>
     <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="49">
-        <v>988382</v>
+        <v>972010</v>
       </c>
       <c r="B37" s="49">
         <v>996169</v>
@@ -4761,7 +4751,7 @@
     </row>
     <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="49">
-        <v>988741</v>
+        <v>972018</v>
       </c>
       <c r="B38" s="49">
         <v>986121</v>
@@ -4838,7 +4828,7 @@
     </row>
     <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A39" s="49">
-        <v>992359</v>
+        <v>972073</v>
       </c>
       <c r="B39" s="49">
         <v>998201</v>
@@ -4915,7 +4905,7 @@
     </row>
     <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A40" s="49">
-        <v>979015</v>
+        <v>974005</v>
       </c>
       <c r="B40" s="49">
         <v>992410</v>
@@ -4992,7 +4982,7 @@
     </row>
     <row r="41" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A41" s="49">
-        <v>982009</v>
+        <v>975048</v>
       </c>
       <c r="B41" s="49">
         <v>986178</v>
@@ -5069,7 +5059,7 @@
     </row>
     <row r="42" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A42" s="49">
-        <v>988002</v>
+        <v>975070</v>
       </c>
       <c r="B42" s="49">
         <v>988077</v>
@@ -5146,7 +5136,7 @@
     </row>
     <row r="43" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A43" s="49">
-        <v>988711</v>
+        <v>975113</v>
       </c>
       <c r="B43" s="49">
         <v>972059</v>
@@ -5223,7 +5213,7 @@
     </row>
     <row r="44" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A44" s="49">
-        <v>988027</v>
+        <v>975145</v>
       </c>
       <c r="B44" s="49">
         <v>967046</v>
@@ -5300,7 +5290,7 @@
     </row>
     <row r="45" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A45" s="49">
-        <v>982011</v>
+        <v>975167</v>
       </c>
       <c r="B45" s="49">
         <v>981063</v>
@@ -5377,7 +5367,7 @@
     </row>
     <row r="46" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A46" s="49">
-        <v>995212</v>
+        <v>976077</v>
       </c>
       <c r="B46" s="49">
         <v>986177</v>
@@ -5454,7 +5444,7 @@
     </row>
     <row r="47" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A47" s="49">
-        <v>998068</v>
+        <v>976014</v>
       </c>
       <c r="B47" s="49">
         <v>982225</v>
@@ -5531,7 +5521,7 @@
     </row>
     <row r="48" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A48" s="49">
-        <v>980171</v>
+        <v>976076</v>
       </c>
       <c r="B48" s="49">
         <v>998039</v>
@@ -5608,7 +5598,7 @@
     </row>
     <row r="49" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A49" s="49">
-        <v>988030</v>
+        <v>976091</v>
       </c>
       <c r="B49" s="49">
         <v>955108</v>
@@ -5685,7 +5675,7 @@
     </row>
     <row r="50" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A50" s="49">
-        <v>992114</v>
+        <v>977045</v>
       </c>
       <c r="B50" s="49">
         <v>955162</v>
@@ -5762,7 +5752,7 @@
     </row>
     <row r="51" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A51" s="49">
-        <v>967029</v>
+        <v>978035</v>
       </c>
       <c r="B51" s="49">
         <v>992567</v>
@@ -5839,7 +5829,7 @@
     </row>
     <row r="52" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A52" s="49">
-        <v>992288</v>
+        <v>978036</v>
       </c>
       <c r="B52" s="49">
         <v>991172</v>
@@ -5916,7 +5906,7 @@
     </row>
     <row r="53" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A53" s="49">
-        <v>986478</v>
+        <v>978072</v>
       </c>
       <c r="B53" s="49">
         <v>992106</v>
@@ -5993,7 +5983,7 @@
     </row>
     <row r="54" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A54" s="49">
-        <v>954174</v>
+        <v>978075</v>
       </c>
       <c r="B54" s="49">
         <v>977047</v>
@@ -6070,7 +6060,7 @@
     </row>
     <row r="55" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A55" s="49">
-        <v>966040</v>
+        <v>979015</v>
       </c>
       <c r="B55" s="49">
         <v>992621</v>
@@ -6147,7 +6137,7 @@
     </row>
     <row r="56" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A56" s="49">
-        <v>986207</v>
+        <v>979030</v>
       </c>
       <c r="B56" s="49">
         <v>992728</v>
@@ -6185,6 +6175,9 @@
       <c r="M56" s="49">
         <v>986195</v>
       </c>
+      <c r="N56" s="49">
+        <v>959060</v>
+      </c>
       <c r="O56" s="49">
         <v>981048</v>
       </c>
@@ -6221,7 +6214,7 @@
     </row>
     <row r="57" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A57" s="49">
-        <v>992041</v>
+        <v>980022</v>
       </c>
       <c r="B57" s="49">
         <v>985044</v>
@@ -6259,6 +6252,9 @@
       <c r="M57" s="49">
         <v>988358</v>
       </c>
+      <c r="N57" s="49">
+        <v>995330</v>
+      </c>
       <c r="O57" s="49">
         <v>981089</v>
       </c>
@@ -6295,7 +6291,7 @@
     </row>
     <row r="58" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A58" s="49">
-        <v>981087</v>
+        <v>980053</v>
       </c>
       <c r="B58" s="49">
         <v>992781</v>
@@ -6369,7 +6365,7 @@
     </row>
     <row r="59" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A59" s="49">
-        <v>940068</v>
+        <v>980111</v>
       </c>
       <c r="B59" s="49">
         <v>955112</v>
@@ -6443,7 +6439,7 @@
     </row>
     <row r="60" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A60" s="49">
-        <v>992360</v>
+        <v>980114</v>
       </c>
       <c r="B60" s="49">
         <v>955192</v>
@@ -6517,7 +6513,7 @@
     </row>
     <row r="61" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A61" s="49">
-        <v>960058</v>
+        <v>980116</v>
       </c>
       <c r="B61" s="49">
         <v>955218</v>
@@ -6591,7 +6587,7 @@
     </row>
     <row r="62" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A62" s="49">
-        <v>967032</v>
+        <v>980159</v>
       </c>
       <c r="B62" s="49">
         <v>991018</v>
@@ -6665,7 +6661,7 @@
     </row>
     <row r="63" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A63" s="49">
-        <v>992150</v>
+        <v>980171</v>
       </c>
       <c r="B63" s="49">
         <v>991148</v>
@@ -6739,7 +6735,7 @@
     </row>
     <row r="64" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A64" s="49">
-        <v>992783</v>
+        <v>981087</v>
       </c>
       <c r="B64" s="49">
         <v>986571</v>
@@ -6813,7 +6809,7 @@
     </row>
     <row r="65" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A65" s="49">
-        <v>992617</v>
+        <v>982009</v>
       </c>
       <c r="B65" s="49">
         <v>982092</v>
@@ -6887,7 +6883,7 @@
     </row>
     <row r="66" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A66" s="49">
-        <v>955067</v>
+        <v>982010</v>
       </c>
       <c r="B66" s="49">
         <v>986599</v>
@@ -6961,7 +6957,7 @@
     </row>
     <row r="67" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A67" s="49">
-        <v>988997</v>
+        <v>982011</v>
       </c>
       <c r="B67" s="49">
         <v>992750</v>
@@ -7035,7 +7031,7 @@
     </row>
     <row r="68" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A68" s="49">
-        <v>958020</v>
+        <v>982060</v>
       </c>
       <c r="B68" s="49">
         <v>991117</v>
@@ -7109,7 +7105,7 @@
     </row>
     <row r="69" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A69" s="49">
-        <v>982151</v>
+        <v>982073</v>
       </c>
       <c r="B69" s="49">
         <v>981014</v>
@@ -7183,7 +7179,7 @@
     </row>
     <row r="70" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A70" s="49">
-        <v>986242</v>
+        <v>982130</v>
       </c>
       <c r="B70" s="49">
         <v>988392</v>
@@ -7257,7 +7253,7 @@
     </row>
     <row r="71" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A71" s="49">
-        <v>975167</v>
+        <v>982149</v>
       </c>
       <c r="B71" s="49">
         <v>988426</v>
@@ -7331,7 +7327,7 @@
     </row>
     <row r="72" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A72" s="49">
-        <v>992457</v>
+        <v>982150</v>
       </c>
       <c r="B72" s="49">
         <v>986105</v>
@@ -7405,7 +7401,7 @@
     </row>
     <row r="73" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A73" s="49">
-        <v>996402</v>
+        <v>982151</v>
       </c>
       <c r="B73" s="49">
         <v>992677</v>
@@ -7479,7 +7475,7 @@
     </row>
     <row r="74" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A74" s="49">
-        <v>992736</v>
+        <v>982241</v>
       </c>
       <c r="B74" s="49">
         <v>986009</v>
@@ -7553,7 +7549,7 @@
     </row>
     <row r="75" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A75" s="49">
-        <v>992051</v>
+        <v>983053</v>
       </c>
       <c r="B75" s="49">
         <v>983057</v>
@@ -7627,7 +7623,7 @@
     </row>
     <row r="76" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A76" s="49">
-        <v>996019</v>
+        <v>984083</v>
       </c>
       <c r="B76" s="49">
         <v>979024</v>
@@ -7701,7 +7697,7 @@
     </row>
     <row r="77" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A77" s="49">
-        <v>996072</v>
+        <v>985069</v>
       </c>
       <c r="B77" s="49">
         <v>988076</v>
@@ -7775,7 +7771,7 @@
     </row>
     <row r="78" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A78" s="49">
-        <v>988379</v>
+        <v>986002</v>
       </c>
       <c r="B78" s="49">
         <v>995257</v>
@@ -7849,7 +7845,7 @@
     </row>
     <row r="79" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A79" s="49">
-        <v>991006</v>
+        <v>986013</v>
       </c>
       <c r="B79" s="49">
         <v>996063</v>
@@ -7923,7 +7919,7 @@
     </row>
     <row r="80" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A80" s="49">
-        <v>988009</v>
+        <v>986063</v>
       </c>
       <c r="B80" s="49">
         <v>982094</v>
@@ -7997,7 +7993,7 @@
     </row>
     <row r="81" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A81" s="49">
-        <v>992153</v>
+        <v>986100</v>
       </c>
       <c r="B81" s="49">
         <v>992500</v>
@@ -8071,7 +8067,7 @@
     </row>
     <row r="82" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A82" s="49">
-        <v>995066</v>
+        <v>986115</v>
       </c>
       <c r="B82" s="49">
         <v>986109</v>
@@ -8145,7 +8141,7 @@
     </row>
     <row r="83" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A83" s="49">
-        <v>986193</v>
+        <v>986128</v>
       </c>
       <c r="B83" s="49">
         <v>986282</v>
@@ -8219,7 +8215,7 @@
     </row>
     <row r="84" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A84" s="49">
-        <v>988004</v>
+        <v>986130</v>
       </c>
       <c r="B84" s="49">
         <v>967027</v>
@@ -8293,7 +8289,7 @@
     </row>
     <row r="85" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A85" s="49">
-        <v>980111</v>
+        <v>986131</v>
       </c>
       <c r="B85" s="49">
         <v>992381</v>
@@ -8367,7 +8363,7 @@
     </row>
     <row r="86" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A86" s="49">
-        <v>954147</v>
+        <v>986133</v>
       </c>
       <c r="B86" s="49">
         <v>988101</v>
@@ -8441,7 +8437,7 @@
     </row>
     <row r="87" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A87" s="49">
-        <v>986270</v>
+        <v>986182</v>
       </c>
       <c r="B87" s="49">
         <v>998012</v>
@@ -8515,7 +8511,7 @@
     </row>
     <row r="88" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A88" s="49">
-        <v>992270</v>
+        <v>986187</v>
       </c>
       <c r="B88" s="49">
         <v>998029</v>
@@ -8589,7 +8585,7 @@
     </row>
     <row r="89" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A89" s="49">
-        <v>986258</v>
+        <v>986193</v>
       </c>
       <c r="B89" s="49">
         <v>988485</v>
@@ -8663,7 +8659,7 @@
     </row>
     <row r="90" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A90" s="49">
-        <v>988889</v>
+        <v>986207</v>
       </c>
       <c r="B90" s="49">
         <v>991022</v>
@@ -8737,7 +8733,7 @@
     </row>
     <row r="91" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A91" s="49">
-        <v>982060</v>
+        <v>986238</v>
       </c>
       <c r="B91" s="49">
         <v>986125</v>
@@ -8811,7 +8807,7 @@
     </row>
     <row r="92" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A92" s="49">
-        <v>986238</v>
+        <v>986242</v>
       </c>
       <c r="B92" s="49">
         <v>988424</v>
@@ -8885,7 +8881,7 @@
     </row>
     <row r="93" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A93" s="49">
-        <v>978035</v>
+        <v>986245</v>
       </c>
       <c r="B93" s="49">
         <v>982093</v>
@@ -8959,7 +8955,7 @@
     </row>
     <row r="94" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A94" s="49">
-        <v>986182</v>
+        <v>986248</v>
       </c>
       <c r="B94" s="49">
         <v>986040</v>
@@ -9033,7 +9029,7 @@
     </row>
     <row r="95" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A95" s="49">
-        <v>986245</v>
+        <v>986258</v>
       </c>
       <c r="B95" s="49">
         <v>994056</v>
@@ -9107,7 +9103,7 @@
     </row>
     <row r="96" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A96" s="49">
-        <v>986248</v>
+        <v>986270</v>
       </c>
       <c r="B96" s="49">
         <v>991091</v>
@@ -9181,7 +9177,7 @@
     </row>
     <row r="97" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A97" s="49">
-        <v>988947</v>
+        <v>986274</v>
       </c>
       <c r="B97" s="49">
         <v>986210</v>
@@ -9255,7 +9251,7 @@
     </row>
     <row r="98" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A98" s="49">
-        <v>977045</v>
+        <v>986477</v>
       </c>
       <c r="B98" s="49">
         <v>996048</v>
@@ -9329,7 +9325,7 @@
     </row>
     <row r="99" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A99" s="49">
-        <v>983053</v>
+        <v>986478</v>
       </c>
       <c r="B99" s="49">
         <v>988065</v>
@@ -9403,7 +9399,7 @@
     </row>
     <row r="100" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A100" s="49">
-        <v>960014</v>
+        <v>986580</v>
       </c>
       <c r="B100" s="49">
         <v>988069</v>
@@ -9477,7 +9473,7 @@
     </row>
     <row r="101" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A101" s="49">
-        <v>966069</v>
+        <v>986597</v>
       </c>
       <c r="B101" s="49">
         <v>988418</v>
@@ -9551,7 +9547,7 @@
     </row>
     <row r="102" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A102" s="49">
-        <v>996318</v>
+        <v>940010</v>
       </c>
       <c r="B102" s="49">
         <v>995217</v>
@@ -9625,7 +9621,7 @@
     </row>
     <row r="103" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A103" s="49">
-        <v>960010</v>
+        <v>940012</v>
       </c>
       <c r="B103" s="49">
         <v>982095</v>
@@ -9699,7 +9695,7 @@
     </row>
     <row r="104" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A104" s="49">
-        <v>988034</v>
+        <v>940016</v>
       </c>
       <c r="B104" s="49">
         <v>988766</v>
@@ -9773,7 +9769,7 @@
     </row>
     <row r="105" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A105" s="49">
-        <v>988031</v>
+        <v>940035</v>
       </c>
       <c r="B105" s="49">
         <v>992701</v>
@@ -9808,6 +9804,9 @@
       <c r="L105" s="49">
         <v>989139</v>
       </c>
+      <c r="M105" s="49">
+        <v>976103</v>
+      </c>
       <c r="O105" s="49">
         <v>954224</v>
       </c>
@@ -9844,7 +9843,7 @@
     </row>
     <row r="106" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A106" s="49">
-        <v>954164</v>
+        <v>940063</v>
       </c>
       <c r="B106" s="49">
         <v>954092</v>
@@ -9879,6 +9878,9 @@
       <c r="L106" s="49">
         <v>988080</v>
       </c>
+      <c r="M106" s="49">
+        <v>976107</v>
+      </c>
       <c r="O106" s="49">
         <v>954225</v>
       </c>
@@ -9915,7 +9917,7 @@
     </row>
     <row r="107" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A107" s="49">
-        <v>992006</v>
+        <v>940068</v>
       </c>
       <c r="B107" s="49">
         <v>988073</v>
@@ -9986,7 +9988,7 @@
     </row>
     <row r="108" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A108" s="49">
-        <v>996147</v>
+        <v>940092</v>
       </c>
       <c r="B108" s="49">
         <v>988371</v>
@@ -10057,7 +10059,7 @@
     </row>
     <row r="109" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A109" s="49">
-        <v>992316</v>
+        <v>988002</v>
       </c>
       <c r="B109" s="49">
         <v>992556</v>
@@ -10128,7 +10130,7 @@
     </row>
     <row r="110" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A110" s="49">
-        <v>980159</v>
+        <v>988004</v>
       </c>
       <c r="B110" s="49">
         <v>992614</v>
@@ -10199,7 +10201,7 @@
     </row>
     <row r="111" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A111" s="49">
-        <v>975048</v>
+        <v>988009</v>
       </c>
       <c r="B111" s="49">
         <v>996191</v>
@@ -10270,7 +10272,7 @@
     </row>
     <row r="112" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A112" s="49">
-        <v>989250</v>
+        <v>988011</v>
       </c>
       <c r="B112" s="49">
         <v>988056</v>
@@ -10341,7 +10343,7 @@
     </row>
     <row r="113" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A113" s="49">
-        <v>995204</v>
+        <v>988013</v>
       </c>
       <c r="B113" s="49">
         <v>994005</v>
@@ -10412,7 +10414,7 @@
     </row>
     <row r="114" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A114" s="49">
-        <v>988352</v>
+        <v>988020</v>
       </c>
       <c r="B114" s="49">
         <v>994007</v>
@@ -10483,7 +10485,7 @@
     </row>
     <row r="115" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A115" s="49">
-        <v>954232</v>
+        <v>988024</v>
       </c>
       <c r="B115" s="49">
         <v>994023</v>
@@ -10554,7 +10556,7 @@
     </row>
     <row r="116" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A116" s="49">
-        <v>985069</v>
+        <v>988026</v>
       </c>
       <c r="B116" s="49">
         <v>986134</v>
@@ -10625,7 +10627,7 @@
     </row>
     <row r="117" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A117" s="49">
-        <v>988443</v>
+        <v>988027</v>
       </c>
       <c r="B117" s="49">
         <v>988654</v>
@@ -10696,7 +10698,7 @@
     </row>
     <row r="118" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A118" s="49">
-        <v>992263</v>
+        <v>988030</v>
       </c>
       <c r="B118" s="49">
         <v>989013</v>
@@ -10767,7 +10769,7 @@
     </row>
     <row r="119" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A119" s="49">
-        <v>992378</v>
+        <v>988031</v>
       </c>
       <c r="B119" s="49">
         <v>995190</v>
@@ -10838,7 +10840,7 @@
     </row>
     <row r="120" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A120" s="49">
-        <v>988026</v>
+        <v>988034</v>
       </c>
       <c r="B120" s="49">
         <v>992333</v>
@@ -10909,7 +10911,7 @@
     </row>
     <row r="121" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A121" s="49">
-        <v>986013</v>
+        <v>988038</v>
       </c>
       <c r="B121" s="49">
         <v>996062</v>
@@ -10980,7 +10982,7 @@
     </row>
     <row r="122" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A122" s="49">
-        <v>978075</v>
+        <v>988048</v>
       </c>
       <c r="B122" s="49">
         <v>988608</v>
@@ -11012,6 +11014,9 @@
       <c r="K122" s="49">
         <v>992618</v>
       </c>
+      <c r="L122" s="49">
+        <v>959016</v>
+      </c>
       <c r="O122" s="49">
         <v>995202</v>
       </c>
@@ -11048,7 +11053,7 @@
     </row>
     <row r="123" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A123" s="49">
-        <v>976091</v>
+        <v>988051</v>
       </c>
       <c r="B123" s="49">
         <v>980139</v>
@@ -11080,6 +11085,9 @@
       <c r="K123" s="49">
         <v>986234</v>
       </c>
+      <c r="L123" s="49">
+        <v>959024</v>
+      </c>
       <c r="O123" s="49">
         <v>960023</v>
       </c>
@@ -11116,7 +11124,7 @@
     </row>
     <row r="124" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A124" s="49">
-        <v>988744</v>
+        <v>988054</v>
       </c>
       <c r="B124" s="49">
         <v>989133</v>
@@ -11148,6 +11156,9 @@
       <c r="K124" s="49">
         <v>986032</v>
       </c>
+      <c r="L124" s="49">
+        <v>972083</v>
+      </c>
       <c r="O124" s="49">
         <v>995049</v>
       </c>
@@ -11184,7 +11195,7 @@
     </row>
     <row r="125" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A125" s="49">
-        <v>986002</v>
+        <v>988352</v>
       </c>
       <c r="B125" s="49">
         <v>989135</v>
@@ -11252,7 +11263,7 @@
     </row>
     <row r="126" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A126" s="49">
-        <v>992040</v>
+        <v>988373</v>
       </c>
       <c r="B126" s="49">
         <v>989141</v>
@@ -11320,7 +11331,7 @@
     </row>
     <row r="127" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A127" s="49">
-        <v>995010</v>
+        <v>988375</v>
       </c>
       <c r="B127" s="49">
         <v>988755</v>
@@ -11388,7 +11399,7 @@
     </row>
     <row r="128" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A128" s="49">
-        <v>988725</v>
+        <v>988376</v>
       </c>
       <c r="B128" s="49">
         <v>975058</v>
@@ -11456,7 +11467,7 @@
     </row>
     <row r="129" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A129" s="49">
-        <v>992193</v>
+        <v>988378</v>
       </c>
       <c r="B129" s="49">
         <v>954057</v>
@@ -11524,7 +11535,7 @@
     </row>
     <row r="130" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A130" s="49">
-        <v>995234</v>
+        <v>988379</v>
       </c>
       <c r="B130" s="49">
         <v>994090</v>
@@ -11592,7 +11603,7 @@
     </row>
     <row r="131" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A131" s="49">
-        <v>954217</v>
+        <v>988382</v>
       </c>
       <c r="B131" s="49">
         <v>992352</v>
@@ -11660,7 +11671,7 @@
     </row>
     <row r="132" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A132" s="49">
-        <v>986597</v>
+        <v>988406</v>
       </c>
       <c r="B132" s="49">
         <v>988364</v>
@@ -11728,7 +11739,7 @@
     </row>
     <row r="133" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A133" s="49">
-        <v>972073</v>
+        <v>988443</v>
       </c>
       <c r="B133" s="49">
         <v>972045</v>
@@ -11796,7 +11807,7 @@
     </row>
     <row r="134" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A134" s="49">
-        <v>986128</v>
+        <v>988477</v>
       </c>
       <c r="B134" s="49">
         <v>972012</v>
@@ -11864,7 +11875,7 @@
     </row>
     <row r="135" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A135" s="49">
-        <v>986100</v>
+        <v>988711</v>
       </c>
       <c r="B135" s="49">
         <v>972036</v>
@@ -11932,7 +11943,7 @@
     </row>
     <row r="136" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A136" s="49">
-        <v>992171</v>
+        <v>988712</v>
       </c>
       <c r="B136" s="49">
         <v>984119</v>
@@ -12000,7 +12011,7 @@
     </row>
     <row r="137" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A137" s="49">
-        <v>995101</v>
+        <v>988719</v>
       </c>
       <c r="B137" s="49">
         <v>977041</v>
@@ -12068,7 +12079,7 @@
     </row>
     <row r="138" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A138" s="49">
-        <v>960043</v>
+        <v>988725</v>
       </c>
       <c r="B138" s="49">
         <v>977039</v>
@@ -12136,7 +12147,7 @@
     </row>
     <row r="139" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A139" s="49">
-        <v>954226</v>
+        <v>988726</v>
       </c>
       <c r="B139" s="49">
         <v>998156</v>
@@ -12204,7 +12215,7 @@
     </row>
     <row r="140" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A140" s="49">
-        <v>988719</v>
+        <v>988739</v>
       </c>
       <c r="B140" s="49">
         <v>940065</v>
@@ -12272,7 +12283,7 @@
     </row>
     <row r="141" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A141" s="49">
-        <v>982130</v>
+        <v>988741</v>
       </c>
       <c r="B141" s="49">
         <v>968017</v>
@@ -12340,7 +12351,7 @@
     </row>
     <row r="142" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A142" s="49">
-        <v>986131</v>
+        <v>988744</v>
       </c>
       <c r="B142" s="49">
         <v>986591</v>
@@ -12408,7 +12419,7 @@
     </row>
     <row r="143" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A143" s="49">
-        <v>954134</v>
+        <v>988746</v>
       </c>
       <c r="B143" s="49">
         <v>991146</v>
@@ -12476,7 +12487,7 @@
     </row>
     <row r="144" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A144" s="49">
-        <v>954013</v>
+        <v>988889</v>
       </c>
       <c r="B144" s="49">
         <v>979052</v>
@@ -12544,7 +12555,7 @@
     </row>
     <row r="145" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A145" s="49">
-        <v>954208</v>
+        <v>988890</v>
       </c>
       <c r="B145" s="49">
         <v>975161</v>
@@ -12612,7 +12623,7 @@
     </row>
     <row r="146" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A146" s="49">
-        <v>954106</v>
+        <v>988899</v>
       </c>
       <c r="B146" s="49">
         <v>982007</v>
@@ -12680,7 +12691,7 @@
     </row>
     <row r="147" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A147" s="49">
-        <v>996166</v>
+        <v>988929</v>
       </c>
       <c r="B147" s="49">
         <v>996141</v>
@@ -12748,7 +12759,7 @@
     </row>
     <row r="148" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A148" s="49">
-        <v>940012</v>
+        <v>988930</v>
       </c>
       <c r="B148" s="49">
         <v>996180</v>
@@ -12813,7 +12824,7 @@
     </row>
     <row r="149" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A149" s="49">
-        <v>996013</v>
+        <v>988947</v>
       </c>
       <c r="B149" s="49">
         <v>996190</v>
@@ -12878,7 +12889,7 @@
     </row>
     <row r="150" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A150" s="49">
-        <v>940035</v>
+        <v>988956</v>
       </c>
       <c r="B150" s="49">
         <v>988057</v>
@@ -12943,7 +12954,7 @@
     </row>
     <row r="151" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A151" s="49">
-        <v>998164</v>
+        <v>988959</v>
       </c>
       <c r="B151" s="49">
         <v>986494</v>
@@ -12978,6 +12989,9 @@
       <c r="O151" s="49">
         <v>955109</v>
       </c>
+      <c r="P151" s="49">
+        <v>959004</v>
+      </c>
       <c r="Q151" s="49">
         <v>988598</v>
       </c>
@@ -13005,7 +13019,7 @@
     </row>
     <row r="152" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A152" s="49">
-        <v>986133</v>
+        <v>988997</v>
       </c>
       <c r="B152" s="49">
         <v>954137</v>
@@ -13040,6 +13054,9 @@
       <c r="O152" s="49">
         <v>955024</v>
       </c>
+      <c r="P152" s="49">
+        <v>959009</v>
+      </c>
       <c r="Q152" s="49">
         <v>989026</v>
       </c>
@@ -13067,7 +13084,7 @@
     </row>
     <row r="153" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A153" s="49">
-        <v>974005</v>
+        <v>989022</v>
       </c>
       <c r="B153" s="49">
         <v>988601</v>
@@ -13102,6 +13119,9 @@
       <c r="O153" s="49">
         <v>992676</v>
       </c>
+      <c r="P153" s="49">
+        <v>959031</v>
+      </c>
       <c r="Q153" s="49">
         <v>954186</v>
       </c>
@@ -13129,7 +13149,7 @@
     </row>
     <row r="154" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A154" s="49">
-        <v>986115</v>
+        <v>989216</v>
       </c>
       <c r="B154" s="49">
         <v>954220</v>
@@ -13164,6 +13184,9 @@
       <c r="O154" s="49">
         <v>984081</v>
       </c>
+      <c r="P154" s="49">
+        <v>959059</v>
+      </c>
       <c r="Q154" s="49">
         <v>966156</v>
       </c>
@@ -13191,7 +13214,7 @@
     </row>
     <row r="155" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A155" s="49">
-        <v>986580</v>
+        <v>989250</v>
       </c>
       <c r="B155" s="49">
         <v>998064</v>
@@ -13226,6 +13249,9 @@
       <c r="O155" s="49">
         <v>992082</v>
       </c>
+      <c r="P155" s="49">
+        <v>975196</v>
+      </c>
       <c r="Q155" s="49">
         <v>989084</v>
       </c>
@@ -13253,7 +13279,7 @@
     </row>
     <row r="156" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A156" s="49">
-        <v>940010</v>
+        <v>989232</v>
       </c>
       <c r="B156" s="49">
         <v>992188</v>
@@ -13315,7 +13341,7 @@
     </row>
     <row r="157" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A157" s="49">
-        <v>988899</v>
+        <v>991006</v>
       </c>
       <c r="B157" s="49">
         <v>992355</v>
@@ -13341,6 +13367,9 @@
       <c r="I157" s="49">
         <v>991039</v>
       </c>
+      <c r="J157" s="49">
+        <v>959054</v>
+      </c>
       <c r="K157" s="49">
         <v>991171</v>
       </c>
@@ -13374,7 +13403,7 @@
     </row>
     <row r="158" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A158" s="49">
-        <v>988959</v>
+        <v>991010</v>
       </c>
       <c r="B158" s="49">
         <v>992005</v>
@@ -13400,6 +13429,9 @@
       <c r="I158" s="49">
         <v>988492</v>
       </c>
+      <c r="J158" s="49">
+        <v>971100</v>
+      </c>
       <c r="K158" s="49">
         <v>988906</v>
       </c>
@@ -13433,7 +13465,7 @@
     </row>
     <row r="159" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A159" s="49">
-        <v>989232</v>
+        <v>991052</v>
       </c>
       <c r="B159" s="49">
         <v>996179</v>
@@ -13492,7 +13524,7 @@
     </row>
     <row r="160" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A160" s="49">
-        <v>992054</v>
+        <v>991165</v>
       </c>
       <c r="B160" s="49">
         <v>954116</v>
@@ -13551,7 +13583,7 @@
     </row>
     <row r="161" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A161" s="49">
-        <v>992129</v>
+        <v>991176</v>
       </c>
       <c r="B161" s="49">
         <v>992662</v>
@@ -13574,6 +13606,9 @@
       <c r="H161" s="49">
         <v>988114</v>
       </c>
+      <c r="I161" s="49">
+        <v>959020</v>
+      </c>
       <c r="K161" s="49">
         <v>995037</v>
       </c>
@@ -13607,7 +13642,7 @@
     </row>
     <row r="162" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A162" s="49">
-        <v>976014</v>
+        <v>992059</v>
       </c>
       <c r="B162" s="49">
         <v>992319</v>
@@ -13630,6 +13665,9 @@
       <c r="H162" s="49">
         <v>988133</v>
       </c>
+      <c r="I162" s="49">
+        <v>972050</v>
+      </c>
       <c r="K162" s="49">
         <v>990052</v>
       </c>
@@ -13663,7 +13701,7 @@
     </row>
     <row r="163" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A163" s="49">
-        <v>958004</v>
+        <v>992698</v>
       </c>
       <c r="B163" s="49">
         <v>975115</v>
@@ -13686,6 +13724,9 @@
       <c r="H163" s="49">
         <v>988496</v>
       </c>
+      <c r="I163" s="49">
+        <v>986610</v>
+      </c>
       <c r="K163" s="49">
         <v>988473</v>
       </c>
@@ -13719,7 +13760,7 @@
     </row>
     <row r="164" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A164" s="49">
-        <v>976076</v>
+        <v>992051</v>
       </c>
       <c r="B164" s="49">
         <v>989157</v>
@@ -13730,6 +13771,9 @@
       <c r="D164" s="49">
         <v>993039</v>
       </c>
+      <c r="E164" s="49">
+        <v>956037</v>
+      </c>
       <c r="F164" s="49">
         <v>993142</v>
       </c>
@@ -13739,6 +13783,9 @@
       <c r="H164" s="49">
         <v>988511</v>
       </c>
+      <c r="I164" s="49">
+        <v>940109</v>
+      </c>
       <c r="K164" s="49">
         <v>992521</v>
       </c>
@@ -13772,7 +13819,7 @@
     </row>
     <row r="165" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A165" s="49">
-        <v>992175</v>
+        <v>992054</v>
       </c>
       <c r="B165" s="49">
         <v>989265</v>
@@ -13783,6 +13830,9 @@
       <c r="D165" s="49">
         <v>992467</v>
       </c>
+      <c r="E165" s="49">
+        <v>959037</v>
+      </c>
       <c r="F165" s="49">
         <v>998004</v>
       </c>
@@ -13792,6 +13842,9 @@
       <c r="H165" s="49">
         <v>988915</v>
       </c>
+      <c r="I165" s="49">
+        <v>992815</v>
+      </c>
       <c r="K165" s="49">
         <v>992709</v>
       </c>
@@ -13825,7 +13878,7 @@
     </row>
     <row r="166" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A166" s="49">
-        <v>995008</v>
+        <v>992592</v>
       </c>
       <c r="B166" s="49">
         <v>989129</v>
@@ -13836,6 +13889,9 @@
       <c r="D166" s="49">
         <v>966210</v>
       </c>
+      <c r="E166" s="49">
+        <v>959038</v>
+      </c>
       <c r="F166" s="49">
         <v>988507</v>
       </c>
@@ -13878,7 +13934,7 @@
     </row>
     <row r="167" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A167" s="49">
-        <v>982241</v>
+        <v>992076</v>
       </c>
       <c r="B167" s="49">
         <v>989130</v>
@@ -13889,6 +13945,9 @@
       <c r="D167" s="49">
         <v>967028</v>
       </c>
+      <c r="E167" s="49">
+        <v>959039</v>
+      </c>
       <c r="F167" s="49">
         <v>995182</v>
       </c>
@@ -13931,7 +13990,7 @@
     </row>
     <row r="168" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A168" s="49">
-        <v>984083</v>
+        <v>992359</v>
       </c>
       <c r="B168" s="49">
         <v>993005</v>
@@ -13942,6 +14001,9 @@
       <c r="D168" s="49">
         <v>986231</v>
       </c>
+      <c r="E168" s="49">
+        <v>959041</v>
+      </c>
       <c r="F168" s="49">
         <v>982161</v>
       </c>
@@ -13984,7 +14046,7 @@
     </row>
     <row r="169" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A169" s="49">
-        <v>993118</v>
+        <v>992408</v>
       </c>
       <c r="B169" s="49">
         <v>995238</v>
@@ -13995,6 +14057,9 @@
       <c r="D169" s="49">
         <v>985067</v>
       </c>
+      <c r="E169" s="49">
+        <v>959049</v>
+      </c>
       <c r="F169" s="49">
         <v>975031</v>
       </c>
@@ -14037,7 +14102,7 @@
     </row>
     <row r="170" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A170" s="49">
-        <v>986130</v>
+        <v>992454</v>
       </c>
       <c r="B170" s="49">
         <v>998081</v>
@@ -14090,7 +14155,7 @@
     </row>
     <row r="171" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A171" s="49">
-        <v>967033</v>
+        <v>992006</v>
       </c>
       <c r="B171" s="49">
         <v>954136</v>
@@ -14104,6 +14169,9 @@
       <c r="F171" s="49">
         <v>991033</v>
       </c>
+      <c r="G171" s="49">
+        <v>959018</v>
+      </c>
       <c r="H171" s="49">
         <v>986284</v>
       </c>
@@ -14140,7 +14208,7 @@
     </row>
     <row r="172" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A172" s="49">
-        <v>986187</v>
+        <v>992378</v>
       </c>
       <c r="B172" s="49">
         <v>981004</v>
@@ -14154,6 +14222,9 @@
       <c r="F172" s="49">
         <v>992135</v>
       </c>
+      <c r="G172" s="49">
+        <v>959023</v>
+      </c>
       <c r="H172" s="49">
         <v>995241</v>
       </c>
@@ -14187,7 +14258,7 @@
     </row>
     <row r="173" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A173" s="49">
-        <v>988930</v>
+        <v>992041</v>
       </c>
       <c r="B173" s="49">
         <v>982006</v>
@@ -14201,6 +14272,9 @@
       <c r="F173" s="49">
         <v>991008</v>
       </c>
+      <c r="G173" s="49">
+        <v>959043</v>
+      </c>
       <c r="H173" s="49">
         <v>985086</v>
       </c>
@@ -14234,7 +14308,7 @@
     </row>
     <row r="174" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A174" s="49">
-        <v>992408</v>
+        <v>992153</v>
       </c>
       <c r="B174" s="49">
         <v>995320</v>
@@ -14248,6 +14322,9 @@
       <c r="F174" s="49">
         <v>989263</v>
       </c>
+      <c r="G174" s="49">
+        <v>977051</v>
+      </c>
       <c r="H174" s="49">
         <v>998161</v>
       </c>
@@ -14281,7 +14358,7 @@
     </row>
     <row r="175" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A175" s="49">
-        <v>992490</v>
+        <v>992457</v>
       </c>
       <c r="B175" s="49">
         <v>966195</v>
@@ -14328,7 +14405,7 @@
     </row>
     <row r="176" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A176" s="49">
-        <v>992240</v>
+        <v>992490</v>
       </c>
       <c r="B176" s="49">
         <v>954269</v>
@@ -14375,7 +14452,7 @@
     </row>
     <row r="177" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A177" s="49">
-        <v>986274</v>
+        <v>992736</v>
       </c>
       <c r="B177" s="49">
         <v>998202</v>
@@ -14422,7 +14499,7 @@
     </row>
     <row r="178" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A178" s="49">
-        <v>988746</v>
+        <v>992150</v>
       </c>
       <c r="B178" s="49">
         <v>954121</v>
@@ -14469,7 +14546,7 @@
     </row>
     <row r="179" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A179" s="49">
-        <v>995025</v>
+        <v>992040</v>
       </c>
       <c r="B179" s="49">
         <v>955081</v>
@@ -14516,7 +14593,7 @@
     </row>
     <row r="180" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A180" s="49">
-        <v>995020</v>
+        <v>992114</v>
       </c>
       <c r="B180" s="49">
         <v>954292</v>
@@ -14563,7 +14640,7 @@
     </row>
     <row r="181" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A181" s="49">
-        <v>995021</v>
+        <v>992512</v>
       </c>
       <c r="B181" s="49">
         <v>954275</v>
@@ -14610,7 +14687,7 @@
     </row>
     <row r="182" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A182" s="49">
-        <v>988406</v>
+        <v>992240</v>
       </c>
       <c r="B182" s="49">
         <v>975003</v>
@@ -14657,7 +14734,7 @@
     </row>
     <row r="183" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A183" s="49">
-        <v>975070</v>
+        <v>992316</v>
       </c>
       <c r="B183" s="49">
         <v>975097</v>
@@ -14704,7 +14781,7 @@
     </row>
     <row r="184" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A184" s="49">
-        <v>986477</v>
+        <v>992672</v>
       </c>
       <c r="B184" s="49">
         <v>975011</v>
@@ -14751,11 +14828,14 @@
     </row>
     <row r="185" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A185" s="49">
-        <v>978072</v>
+        <v>992152</v>
       </c>
       <c r="B185" s="49">
         <v>956014</v>
       </c>
+      <c r="C185" s="49">
+        <v>959053</v>
+      </c>
       <c r="D185" s="49">
         <v>992549</v>
       </c>
@@ -14795,7 +14875,7 @@
     </row>
     <row r="186" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A186" s="49">
-        <v>954004</v>
+        <v>992129</v>
       </c>
       <c r="B186" s="49">
         <v>954043</v>
@@ -14839,7 +14919,7 @@
     </row>
     <row r="187" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A187" s="49">
-        <v>982150</v>
+        <v>992171</v>
       </c>
       <c r="B187" s="49">
         <v>990065</v>
@@ -14883,7 +14963,7 @@
     </row>
     <row r="188" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A188" s="49">
-        <v>988011</v>
+        <v>992193</v>
       </c>
       <c r="B188" s="49">
         <v>996381</v>
@@ -14927,7 +15007,7 @@
     </row>
     <row r="189" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A189" s="49">
-        <v>988024</v>
+        <v>992175</v>
       </c>
       <c r="B189" s="49">
         <v>986590</v>
@@ -14971,7 +15051,7 @@
     </row>
     <row r="190" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A190" s="49">
-        <v>988038</v>
+        <v>992360</v>
       </c>
       <c r="B190" s="49">
         <v>980055</v>
@@ -15015,7 +15095,7 @@
     </row>
     <row r="191" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A191" s="49">
-        <v>988054</v>
+        <v>992783</v>
       </c>
       <c r="B191" s="49">
         <v>996142</v>
@@ -15059,7 +15139,7 @@
     </row>
     <row r="192" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A192" s="49">
-        <v>995229</v>
+        <v>992263</v>
       </c>
       <c r="B192" s="49">
         <v>980165</v>
@@ -15103,7 +15183,7 @@
     </row>
     <row r="193" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A193" s="49">
-        <v>995236</v>
+        <v>992270</v>
       </c>
       <c r="B193" s="49">
         <v>996145</v>
@@ -15147,7 +15227,7 @@
     </row>
     <row r="194" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A194" s="49">
-        <v>998040</v>
+        <v>992617</v>
       </c>
       <c r="B194" s="49">
         <v>986166</v>
@@ -15191,7 +15271,7 @@
     </row>
     <row r="195" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A195" s="49">
-        <v>988712</v>
+        <v>992288</v>
       </c>
       <c r="B195" s="49">
         <v>992078</v>
@@ -15235,7 +15315,7 @@
     </row>
     <row r="196" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A196" s="49">
-        <v>954285</v>
+        <v>993051</v>
       </c>
       <c r="B196" s="49">
         <v>988481</v>
@@ -15279,7 +15359,7 @@
     </row>
     <row r="197" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A197" s="49">
-        <v>982149</v>
+        <v>993087</v>
       </c>
       <c r="B197" s="49">
         <v>996143</v>
@@ -15323,7 +15403,7 @@
     </row>
     <row r="198" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A198" s="49">
-        <v>992152</v>
+        <v>993095</v>
       </c>
       <c r="B198" s="49">
         <v>998104</v>
@@ -15367,7 +15447,7 @@
     </row>
     <row r="199" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A199" s="49">
-        <v>980022</v>
+        <v>993118</v>
       </c>
       <c r="B199" s="49">
         <v>988428</v>
@@ -15411,7 +15491,7 @@
     </row>
     <row r="200" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A200" s="49">
-        <v>995225</v>
+        <v>993124</v>
       </c>
       <c r="B200" s="49">
         <v>996155</v>
@@ -15455,7 +15535,7 @@
     </row>
     <row r="201" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A201" s="49">
-        <v>982073</v>
+        <v>995008</v>
       </c>
       <c r="B201" s="49">
         <v>986495</v>
@@ -15499,7 +15579,7 @@
     </row>
     <row r="202" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A202" s="49">
-        <v>954112</v>
+        <v>995010</v>
       </c>
       <c r="B202" s="49">
         <v>992272</v>
@@ -15543,7 +15623,7 @@
     </row>
     <row r="203" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A203" s="49">
-        <v>980116</v>
+        <v>995011</v>
       </c>
       <c r="B203" s="49">
         <v>995293</v>
@@ -15587,7 +15667,7 @@
     </row>
     <row r="204" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A204" s="49">
-        <v>988929</v>
+        <v>995020</v>
       </c>
       <c r="B204" s="49">
         <v>996111</v>
@@ -15631,7 +15711,7 @@
     </row>
     <row r="205" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A205" s="49">
-        <v>991176</v>
+        <v>995021</v>
       </c>
       <c r="B205" s="49">
         <v>954108</v>
@@ -15675,7 +15755,7 @@
     </row>
     <row r="206" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A206" s="49">
-        <v>992672</v>
+        <v>995025</v>
       </c>
       <c r="B206" s="49">
         <v>996144</v>
@@ -15719,7 +15799,7 @@
     </row>
     <row r="207" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A207" s="49">
-        <v>993051</v>
+        <v>995066</v>
       </c>
       <c r="B207" s="49">
         <v>954131</v>
@@ -15763,7 +15843,7 @@
     </row>
     <row r="208" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A208" s="49">
-        <v>993095</v>
+        <v>995101</v>
       </c>
       <c r="B208" s="49">
         <v>954132</v>
@@ -15807,7 +15887,7 @@
     </row>
     <row r="209" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A209" s="49">
-        <v>940092</v>
+        <v>995109</v>
       </c>
       <c r="B209" s="49">
         <v>992588</v>
@@ -15851,7 +15931,7 @@
     </row>
     <row r="210" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A210" s="49">
-        <v>989022</v>
+        <v>995197</v>
       </c>
       <c r="B210" s="49">
         <v>972031</v>
@@ -15895,7 +15975,7 @@
     </row>
     <row r="211" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A211" s="49">
-        <v>954074</v>
+        <v>995204</v>
       </c>
       <c r="B211" s="49">
         <v>954130</v>
@@ -15939,7 +16019,7 @@
     </row>
     <row r="212" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A212" s="49">
-        <v>954109</v>
+        <v>995212</v>
       </c>
       <c r="B212" s="49">
         <v>986275</v>
@@ -15983,7 +16063,7 @@
     </row>
     <row r="213" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A213" s="49">
-        <v>978036</v>
+        <v>995225</v>
       </c>
       <c r="B213" s="49">
         <v>986563</v>
@@ -16027,7 +16107,7 @@
     </row>
     <row r="214" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A214" s="49">
-        <v>966041</v>
+        <v>995229</v>
       </c>
       <c r="B214" s="49">
         <v>986139</v>
@@ -16071,7 +16151,7 @@
     </row>
     <row r="215" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A215" s="49">
-        <v>979030</v>
+        <v>995232</v>
       </c>
       <c r="B215" s="49">
         <v>954064</v>
@@ -16115,7 +16195,7 @@
     </row>
     <row r="216" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A216" s="49">
-        <v>988373</v>
+        <v>995234</v>
       </c>
       <c r="B216" s="49">
         <v>954133</v>
@@ -16159,7 +16239,7 @@
     </row>
     <row r="217" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A217" s="49">
-        <v>988051</v>
+        <v>995236</v>
       </c>
       <c r="B217" s="49">
         <v>954162</v>
@@ -16203,7 +16283,7 @@
     </row>
     <row r="218" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A218" s="49">
-        <v>988890</v>
+        <v>995325</v>
       </c>
       <c r="B218" s="49">
         <v>992160</v>
@@ -16247,7 +16327,7 @@
     </row>
     <row r="219" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A219" s="49">
-        <v>988477</v>
+        <v>996013</v>
       </c>
       <c r="B219" s="49">
         <v>982099</v>
@@ -16291,7 +16371,7 @@
     </row>
     <row r="220" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A220" s="49">
-        <v>966214</v>
+        <v>996019</v>
       </c>
       <c r="B220" s="49">
         <v>982100</v>
@@ -16335,7 +16415,7 @@
     </row>
     <row r="221" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A221" s="49">
-        <v>992592</v>
+        <v>996021</v>
       </c>
       <c r="B221" s="49">
         <v>982101</v>
@@ -16379,7 +16459,7 @@
     </row>
     <row r="222" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A222" s="49">
-        <v>972050</v>
+        <v>996022</v>
       </c>
       <c r="B222" s="49">
         <v>992436</v>
@@ -16423,7 +16503,7 @@
     </row>
     <row r="223" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A223" s="49">
-        <v>968015</v>
+        <v>996023</v>
       </c>
       <c r="B223" s="49">
         <v>992223</v>
@@ -16467,7 +16547,7 @@
     </row>
     <row r="224" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A224" s="49">
-        <v>940016</v>
+        <v>996026</v>
       </c>
       <c r="B224" s="49">
         <v>992293</v>
@@ -16511,7 +16591,7 @@
     </row>
     <row r="225" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A225" s="49">
-        <v>988726</v>
+        <v>996072</v>
       </c>
       <c r="B225" s="49">
         <v>998122</v>
@@ -16555,7 +16635,7 @@
     </row>
     <row r="226" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A226" s="49">
-        <v>988020</v>
+        <v>996147</v>
       </c>
       <c r="B226" s="49">
         <v>975178</v>
@@ -16599,7 +16679,7 @@
     </row>
     <row r="227" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A227" s="49">
-        <v>980053</v>
+        <v>996166</v>
       </c>
       <c r="B227" s="49">
         <v>954181</v>
@@ -16643,7 +16723,7 @@
     </row>
     <row r="228" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A228" s="49">
-        <v>975113</v>
+        <v>996318</v>
       </c>
       <c r="B228" s="49">
         <v>988099</v>
@@ -16687,7 +16767,7 @@
     </row>
     <row r="229" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A229" s="49">
-        <v>992512</v>
+        <v>996385</v>
       </c>
       <c r="B229" s="49">
         <v>955077</v>
@@ -16731,7 +16811,7 @@
     </row>
     <row r="230" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A230" s="49">
-        <v>988375</v>
+        <v>996401</v>
       </c>
       <c r="B230" s="49">
         <v>954114</v>
@@ -16775,7 +16855,7 @@
     </row>
     <row r="231" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A231" s="49">
-        <v>954055</v>
+        <v>996402</v>
       </c>
       <c r="B231" s="49">
         <v>955117</v>
@@ -16819,7 +16899,7 @@
     </row>
     <row r="232" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A232" s="49">
-        <v>995011</v>
+        <v>998040</v>
       </c>
       <c r="B232" s="49">
         <v>995291</v>
@@ -16863,7 +16943,7 @@
     </row>
     <row r="233" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A233" s="49">
-        <v>991052</v>
+        <v>998068</v>
       </c>
       <c r="B233" s="49">
         <v>972072</v>
@@ -16907,7 +16987,7 @@
     </row>
     <row r="234" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A234" s="49">
-        <v>988376</v>
+        <v>998164</v>
       </c>
       <c r="B234" s="49">
         <v>972076</v>
@@ -16950,6 +17030,9 @@
       </c>
     </row>
     <row r="235" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A235" s="49">
+        <v>954004</v>
+      </c>
       <c r="B235" s="49">
         <v>967041</v>
       </c>
@@ -16991,6 +17074,9 @@
       </c>
     </row>
     <row r="236" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="A236" s="49">
+        <v>954013</v>
+      </c>
       <c r="B236" s="49">
         <v>940054</v>
       </c>
@@ -17035,6 +17121,9 @@
       <c r="B237" s="49">
         <v>992788</v>
       </c>
+      <c r="D237" s="49">
+        <v>959063</v>
+      </c>
       <c r="F237" s="49">
         <v>988774</v>
       </c>
@@ -17073,6 +17162,9 @@
       <c r="B238" s="49">
         <v>984051</v>
       </c>
+      <c r="D238" s="49">
+        <v>962011</v>
+      </c>
       <c r="F238" s="49">
         <v>991181</v>
       </c>
@@ -17111,6 +17203,9 @@
       <c r="B239" s="49">
         <v>986014</v>
       </c>
+      <c r="D239" s="49">
+        <v>963005</v>
+      </c>
       <c r="F239" s="49">
         <v>960045</v>
       </c>
@@ -18751,6 +18846,9 @@
       <c r="H282" s="49">
         <v>980176</v>
       </c>
+      <c r="K282" s="49">
+        <v>954293</v>
+      </c>
       <c r="Q282" s="49">
         <v>992329</v>
       </c>
@@ -18786,6 +18884,9 @@
       <c r="H283" s="49">
         <v>986564</v>
       </c>
+      <c r="K283" s="49">
+        <v>959012</v>
+      </c>
       <c r="Q283" s="49">
         <v>992590</v>
       </c>
@@ -18821,6 +18922,9 @@
       <c r="H284" s="49">
         <v>992422</v>
       </c>
+      <c r="K284" s="49">
+        <v>959035</v>
+      </c>
       <c r="Q284" s="49">
         <v>996121</v>
       </c>
@@ -18856,6 +18960,9 @@
       <c r="H285" s="49">
         <v>989017</v>
       </c>
+      <c r="K285" s="49">
+        <v>959050</v>
+      </c>
       <c r="Q285" s="49">
         <v>996127</v>
       </c>
@@ -18876,6 +18983,9 @@
       </c>
       <c r="W285" s="49">
         <v>986521</v>
+      </c>
+      <c r="X285" s="49">
+        <v>954295</v>
       </c>
     </row>
     <row r="286" spans="2:24" x14ac:dyDescent="0.3">
@@ -18888,6 +18998,9 @@
       <c r="H286" s="49">
         <v>982038</v>
       </c>
+      <c r="K286" s="49">
+        <v>976101</v>
+      </c>
       <c r="Q286" s="49">
         <v>996130</v>
       </c>
@@ -18908,6 +19021,9 @@
       </c>
       <c r="W286" s="49">
         <v>998043</v>
+      </c>
+      <c r="X286" s="49">
+        <v>959011</v>
       </c>
     </row>
     <row r="287" spans="2:24" x14ac:dyDescent="0.3">
@@ -18920,6 +19036,9 @@
       <c r="H287" s="49">
         <v>992205</v>
       </c>
+      <c r="K287" s="49">
+        <v>986609</v>
+      </c>
       <c r="Q287" s="49">
         <v>988591</v>
       </c>
@@ -18940,6 +19059,9 @@
       </c>
       <c r="W287" s="49">
         <v>989260</v>
+      </c>
+      <c r="X287" s="49">
+        <v>959057</v>
       </c>
     </row>
     <row r="288" spans="2:24" x14ac:dyDescent="0.3">
@@ -18952,6 +19074,9 @@
       <c r="H288" s="49">
         <v>991142</v>
       </c>
+      <c r="K288" s="49">
+        <v>940111</v>
+      </c>
       <c r="Q288" s="49">
         <v>989116</v>
       </c>
@@ -18972,6 +19097,9 @@
       </c>
       <c r="W288" s="49">
         <v>995084</v>
+      </c>
+      <c r="X288" s="49">
+        <v>959062</v>
       </c>
     </row>
     <row r="289" spans="2:23" x14ac:dyDescent="0.3">
@@ -18984,6 +19112,9 @@
       <c r="H289" s="49">
         <v>968012</v>
       </c>
+      <c r="K289" s="49">
+        <v>991191</v>
+      </c>
       <c r="Q289" s="49">
         <v>979013</v>
       </c>
@@ -19650,6 +19781,9 @@
       <c r="B310" s="49">
         <v>996396</v>
       </c>
+      <c r="F310" s="49">
+        <v>959006</v>
+      </c>
       <c r="H310" s="49">
         <v>954197</v>
       </c>
@@ -19679,6 +19813,9 @@
       <c r="B311" s="49">
         <v>940027</v>
       </c>
+      <c r="F311" s="49">
+        <v>959032</v>
+      </c>
       <c r="H311" s="49">
         <v>996092</v>
       </c>
@@ -19708,6 +19845,9 @@
       <c r="B312" s="49">
         <v>977042</v>
       </c>
+      <c r="F312" s="49">
+        <v>959036</v>
+      </c>
       <c r="H312" s="49">
         <v>998134</v>
       </c>
@@ -19737,6 +19877,9 @@
       <c r="B313" s="49">
         <v>992081</v>
       </c>
+      <c r="F313" s="49">
+        <v>959047</v>
+      </c>
       <c r="H313" s="49">
         <v>954002</v>
       </c>
@@ -19766,6 +19909,9 @@
       <c r="B314" s="49">
         <v>954075</v>
       </c>
+      <c r="F314" s="49">
+        <v>967047</v>
+      </c>
       <c r="H314" s="49">
         <v>960021</v>
       </c>
@@ -19795,6 +19941,9 @@
       <c r="B315" s="49">
         <v>992294</v>
       </c>
+      <c r="F315" s="49">
+        <v>976108</v>
+      </c>
       <c r="H315" s="49">
         <v>988928</v>
       </c>
@@ -19824,6 +19973,9 @@
       <c r="B316" s="49">
         <v>984056</v>
       </c>
+      <c r="F316" s="49">
+        <v>940112</v>
+      </c>
       <c r="H316" s="49">
         <v>996094</v>
       </c>
@@ -19853,6 +20005,9 @@
       <c r="B317" s="49">
         <v>992369</v>
       </c>
+      <c r="F317" s="49">
+        <v>992816</v>
+      </c>
       <c r="H317" s="49">
         <v>955228</v>
       </c>
@@ -20230,6 +20385,9 @@
       <c r="B330" s="49">
         <v>990017</v>
       </c>
+      <c r="H330" s="49">
+        <v>954294</v>
+      </c>
       <c r="Q330" s="49">
         <v>988599</v>
       </c>
@@ -20256,6 +20414,9 @@
       <c r="B331" s="49">
         <v>967008</v>
       </c>
+      <c r="H331" s="49">
+        <v>959056</v>
+      </c>
       <c r="Q331" s="49">
         <v>989219</v>
       </c>
@@ -20282,6 +20443,9 @@
       <c r="B332" s="49">
         <v>982199</v>
       </c>
+      <c r="H332" s="49">
+        <v>940108</v>
+      </c>
       <c r="Q332" s="49">
         <v>989221</v>
       </c>
@@ -20577,6 +20741,9 @@
       <c r="S343" s="49">
         <v>992301</v>
       </c>
+      <c r="T343" s="49">
+        <v>991190</v>
+      </c>
       <c r="U343" s="49">
         <v>954284</v>
       </c>
@@ -20695,6 +20862,9 @@
       <c r="U348" s="49">
         <v>979034</v>
       </c>
+      <c r="V348" s="49">
+        <v>956023</v>
+      </c>
       <c r="W348" s="49">
         <v>993138</v>
       </c>
@@ -20715,6 +20885,9 @@
       <c r="U349" s="49">
         <v>996229</v>
       </c>
+      <c r="V349" s="49">
+        <v>959002</v>
+      </c>
       <c r="W349" s="49">
         <v>986533</v>
       </c>
@@ -20735,6 +20908,9 @@
       <c r="U350" s="49">
         <v>996230</v>
       </c>
+      <c r="V350" s="49">
+        <v>940114</v>
+      </c>
       <c r="W350" s="49">
         <v>998072</v>
       </c>
@@ -20755,6 +20931,9 @@
       <c r="U351" s="49">
         <v>994096</v>
       </c>
+      <c r="V351" s="49">
+        <v>994111</v>
+      </c>
       <c r="W351" s="49">
         <v>986516</v>
       </c>
@@ -20932,6 +21111,9 @@
       <c r="S360" s="49">
         <v>969010</v>
       </c>
+      <c r="U360" s="49">
+        <v>959058</v>
+      </c>
       <c r="W360" s="49">
         <v>996138</v>
       </c>
@@ -20949,6 +21131,9 @@
       <c r="S361" s="49">
         <v>955146</v>
       </c>
+      <c r="U361" s="49">
+        <v>976104</v>
+      </c>
     </row>
     <row r="362" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B362" s="49">
@@ -20963,6 +21148,9 @@
       <c r="S362" s="49">
         <v>992140</v>
       </c>
+      <c r="U362" s="49">
+        <v>976106</v>
+      </c>
     </row>
     <row r="363" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B363" s="49">
@@ -20977,6 +21165,9 @@
       <c r="S363" s="49">
         <v>992746</v>
       </c>
+      <c r="U363" s="49">
+        <v>981105</v>
+      </c>
     </row>
     <row r="364" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B364" s="49">
@@ -21007,6 +21198,9 @@
       </c>
     </row>
     <row r="366" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B366" s="49">
+        <v>959003</v>
+      </c>
       <c r="Q366" s="49">
         <v>966128</v>
       </c>
@@ -21018,6 +21212,9 @@
       </c>
     </row>
     <row r="367" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B367" s="49">
+        <v>959046</v>
+      </c>
       <c r="Q367" s="49">
         <v>992565</v>
       </c>
@@ -21029,6 +21226,9 @@
       </c>
     </row>
     <row r="368" spans="2:23" x14ac:dyDescent="0.3">
+      <c r="B368" s="49">
+        <v>959052</v>
+      </c>
       <c r="Q368" s="49">
         <v>988814</v>
       </c>
@@ -21039,7 +21239,10 @@
         <v>975004</v>
       </c>
     </row>
-    <row r="369" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="369" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B369" s="49">
+        <v>976023</v>
+      </c>
       <c r="Q369" s="49">
         <v>996132</v>
       </c>
@@ -21050,7 +21253,10 @@
         <v>982049</v>
       </c>
     </row>
-    <row r="370" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="370" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B370" s="49">
+        <v>940115</v>
+      </c>
       <c r="Q370" s="49">
         <v>986353</v>
       </c>
@@ -21061,7 +21267,10 @@
         <v>992407</v>
       </c>
     </row>
-    <row r="371" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="371" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B371" s="49">
+        <v>991188</v>
+      </c>
       <c r="Q371" s="49">
         <v>966148</v>
       </c>
@@ -21072,7 +21281,10 @@
         <v>982053</v>
       </c>
     </row>
-    <row r="372" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="372" spans="2:19" x14ac:dyDescent="0.3">
+      <c r="B372" s="49">
+        <v>992487</v>
+      </c>
       <c r="Q372" s="49">
         <v>986348</v>
       </c>
@@ -21083,7 +21295,7 @@
         <v>954124</v>
       </c>
     </row>
-    <row r="373" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="373" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q373" s="49">
         <v>988822</v>
       </c>
@@ -21094,7 +21306,7 @@
         <v>978013</v>
       </c>
     </row>
-    <row r="374" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="374" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q374" s="49">
         <v>988256</v>
       </c>
@@ -21105,7 +21317,7 @@
         <v>988840</v>
       </c>
     </row>
-    <row r="375" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="375" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q375" s="49">
         <v>966054</v>
       </c>
@@ -21116,7 +21328,7 @@
         <v>984065</v>
       </c>
     </row>
-    <row r="376" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="376" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q376" s="49">
         <v>982018</v>
       </c>
@@ -21127,7 +21339,7 @@
         <v>992345</v>
       </c>
     </row>
-    <row r="377" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="377" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q377" s="49">
         <v>993014</v>
       </c>
@@ -21138,7 +21350,7 @@
         <v>991162</v>
       </c>
     </row>
-    <row r="378" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="378" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q378" s="49">
         <v>966138</v>
       </c>
@@ -21149,7 +21361,7 @@
         <v>996245</v>
       </c>
     </row>
-    <row r="379" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="379" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q379" s="49">
         <v>986349</v>
       </c>
@@ -21160,7 +21372,7 @@
         <v>985021</v>
       </c>
     </row>
-    <row r="380" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="380" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q380" s="49">
         <v>988606</v>
       </c>
@@ -21171,7 +21383,7 @@
         <v>988684</v>
       </c>
     </row>
-    <row r="381" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="381" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q381" s="49">
         <v>988794</v>
       </c>
@@ -21182,7 +21394,7 @@
         <v>993057</v>
       </c>
     </row>
-    <row r="382" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="382" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q382" s="49">
         <v>966039</v>
       </c>
@@ -21193,7 +21405,7 @@
         <v>992546</v>
       </c>
     </row>
-    <row r="383" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="383" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q383" s="49">
         <v>966047</v>
       </c>
@@ -21204,7 +21416,7 @@
         <v>992125</v>
       </c>
     </row>
-    <row r="384" spans="17:19" x14ac:dyDescent="0.3">
+    <row r="384" spans="2:19" x14ac:dyDescent="0.3">
       <c r="Q384" s="49">
         <v>984097</v>
       </c>
@@ -22154,133 +22366,223 @@
       <c r="Q470" s="49">
         <v>993115</v>
       </c>
+      <c r="R470" s="49">
+        <v>955229</v>
+      </c>
+      <c r="S470" s="49">
+        <v>954297</v>
+      </c>
     </row>
     <row r="471" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q471" s="49">
         <v>968003</v>
       </c>
+      <c r="R471" s="49">
+        <v>958032</v>
+      </c>
+      <c r="S471" s="49">
+        <v>955105</v>
+      </c>
     </row>
     <row r="472" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q472" s="49">
         <v>955182</v>
       </c>
+      <c r="R472" s="49">
+        <v>959007</v>
+      </c>
+      <c r="S472" s="49">
+        <v>959010</v>
+      </c>
     </row>
     <row r="473" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q473" s="49">
         <v>988836</v>
       </c>
+      <c r="R473" s="49">
+        <v>959014</v>
+      </c>
+      <c r="S473" s="49">
+        <v>959027</v>
+      </c>
     </row>
     <row r="474" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q474" s="49">
         <v>940090</v>
       </c>
+      <c r="R474" s="49">
+        <v>959028</v>
+      </c>
+      <c r="S474" s="49">
+        <v>959030</v>
+      </c>
     </row>
     <row r="475" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q475" s="49">
         <v>992753</v>
       </c>
+      <c r="R475" s="49">
+        <v>959045</v>
+      </c>
+      <c r="S475" s="49">
+        <v>959034</v>
+      </c>
     </row>
     <row r="476" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q476" s="49">
         <v>955042</v>
       </c>
+      <c r="R476" s="49">
+        <v>959055</v>
+      </c>
+      <c r="S476" s="49">
+        <v>959040</v>
+      </c>
     </row>
     <row r="477" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q477" s="49">
         <v>966034</v>
       </c>
+      <c r="R477" s="49">
+        <v>959061</v>
+      </c>
+      <c r="S477" s="49">
+        <v>959051</v>
+      </c>
     </row>
     <row r="478" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q478" s="49">
         <v>988275</v>
       </c>
+      <c r="R478" s="49">
+        <v>966215</v>
+      </c>
+      <c r="S478" s="49">
+        <v>962012</v>
+      </c>
     </row>
     <row r="479" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q479" s="49">
         <v>982136</v>
       </c>
+      <c r="R479" s="49">
+        <v>976102</v>
+      </c>
+      <c r="S479" s="49">
+        <v>975197</v>
+      </c>
     </row>
     <row r="480" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q480" s="49">
         <v>982137</v>
       </c>
-    </row>
-    <row r="481" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="R480" s="49">
+        <v>984124</v>
+      </c>
+      <c r="S480" s="49">
+        <v>976105</v>
+      </c>
+    </row>
+    <row r="481" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q481" s="49">
         <v>966200</v>
       </c>
-    </row>
-    <row r="482" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="R481" s="49">
+        <v>992814</v>
+      </c>
+      <c r="S481" s="49">
+        <v>976100</v>
+      </c>
+    </row>
+    <row r="482" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q482" s="49">
         <v>988815</v>
       </c>
-    </row>
-    <row r="483" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="S482" s="49">
+        <v>981106</v>
+      </c>
+    </row>
+    <row r="483" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q483" s="49">
         <v>966115</v>
       </c>
-    </row>
-    <row r="484" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="S483" s="49">
+        <v>984123</v>
+      </c>
+    </row>
+    <row r="484" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q484" s="49">
         <v>978070</v>
       </c>
-    </row>
-    <row r="485" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="S484" s="49">
+        <v>940110</v>
+      </c>
+    </row>
+    <row r="485" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q485" s="49">
         <v>993139</v>
       </c>
-    </row>
-    <row r="486" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="S485" s="49">
+        <v>991186</v>
+      </c>
+    </row>
+    <row r="486" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q486" s="49">
         <v>955043</v>
       </c>
-    </row>
-    <row r="487" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="S486" s="49">
+        <v>992817</v>
+      </c>
+    </row>
+    <row r="487" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q487" s="49">
         <v>989112</v>
       </c>
-    </row>
-    <row r="488" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="S487" s="49">
+        <v>992818</v>
+      </c>
+    </row>
+    <row r="488" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q488" s="49">
         <v>993114</v>
       </c>
     </row>
-    <row r="489" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="489" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q489" s="49">
         <v>955155</v>
       </c>
     </row>
-    <row r="490" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="490" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q490" s="49">
         <v>966044</v>
       </c>
     </row>
-    <row r="491" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="491" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q491" s="49">
         <v>981038</v>
       </c>
     </row>
-    <row r="492" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="492" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q492" s="49">
         <v>988838</v>
       </c>
     </row>
-    <row r="493" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="493" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q493" s="49">
         <v>989272</v>
       </c>
     </row>
-    <row r="494" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="494" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q494" s="49">
         <v>966166</v>
       </c>
     </row>
-    <row r="495" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="495" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q495" s="49">
         <v>984077</v>
       </c>
     </row>
-    <row r="496" spans="17:17" x14ac:dyDescent="0.3">
+    <row r="496" spans="17:19" x14ac:dyDescent="0.3">
       <c r="Q496" s="49">
         <v>993079</v>
       </c>
@@ -22593,6 +22895,76 @@
     <row r="558" spans="17:17" x14ac:dyDescent="0.3">
       <c r="Q558" s="49">
         <v>982215</v>
+      </c>
+    </row>
+    <row r="559" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q559" s="49">
+        <v>958031</v>
+      </c>
+    </row>
+    <row r="560" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q560" s="49">
+        <v>959013</v>
+      </c>
+    </row>
+    <row r="561" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q561" s="49">
+        <v>959017</v>
+      </c>
+    </row>
+    <row r="562" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q562" s="49">
+        <v>959019</v>
+      </c>
+    </row>
+    <row r="563" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q563" s="49">
+        <v>959021</v>
+      </c>
+    </row>
+    <row r="564" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q564" s="49">
+        <v>959025</v>
+      </c>
+    </row>
+    <row r="565" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q565" s="49">
+        <v>959042</v>
+      </c>
+    </row>
+    <row r="566" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q566" s="49">
+        <v>959048</v>
+      </c>
+    </row>
+    <row r="567" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q567" s="49">
+        <v>980213</v>
+      </c>
+    </row>
+    <row r="568" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q568" s="49">
+        <v>987018</v>
+      </c>
+    </row>
+    <row r="569" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q569" s="49">
+        <v>987019</v>
+      </c>
+    </row>
+    <row r="570" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q570" s="49">
+        <v>940107</v>
+      </c>
+    </row>
+    <row r="571" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q571" s="49">
+        <v>940113</v>
+      </c>
+    </row>
+    <row r="572" spans="17:17" x14ac:dyDescent="0.3">
+      <c r="Q572" s="49">
+        <v>991187</v>
       </c>
     </row>
   </sheetData>

--- a/GRM_Data.xlsx
+++ b/GRM_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipTime Cloud\Hana Contact Mgr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3C1AE54-6D18-4F4C-BFDB-9F6728731B73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2A19AD-F78A-434C-BBD0-93D4C6C85A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1385" uniqueCount="323">
   <si>
     <t>G7189653</t>
   </si>
@@ -974,9 +974,6 @@
     <t>[2사업단] - 정지혜</t>
   </si>
   <si>
-    <t>[3사업단] - 이선미</t>
-  </si>
-  <si>
     <t>[3사업단] - 조현주</t>
   </si>
   <si>
@@ -1007,6 +1004,18 @@
   </si>
   <si>
     <t>[4사업단] - 박자영</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>G7113274/G7113292/G7141793</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>[3사업단] - 이선미</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>G7247404</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1957,16 +1966,16 @@
         <v>18</v>
       </c>
       <c r="O1" s="49" t="s">
-        <v>267</v>
+        <v>322</v>
       </c>
       <c r="P1" s="49" t="s">
         <v>308</v>
       </c>
       <c r="Q1" s="49" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="R1" s="49" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="S1" s="49" t="s">
         <v>2</v>
@@ -1987,7 +1996,7 @@
         <v>11</v>
       </c>
       <c r="Y1" s="49" t="s">
-        <v>53</v>
+        <v>320</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.3">
@@ -2034,34 +2043,34 @@
         <v>302</v>
       </c>
       <c r="O2" s="49" t="s">
+        <v>321</v>
+      </c>
+      <c r="P2" s="49" t="s">
         <v>311</v>
       </c>
-      <c r="P2" s="49" t="s">
-        <v>312</v>
-      </c>
       <c r="Q2" s="49" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="R2" s="49" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="S2" s="49" t="s">
         <v>303</v>
       </c>
       <c r="T2" s="49" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="U2" s="49" t="s">
         <v>304</v>
       </c>
       <c r="V2" s="49" t="s">
+        <v>317</v>
+      </c>
+      <c r="W2" s="49" t="s">
         <v>318</v>
       </c>
-      <c r="W2" s="49" t="s">
+      <c r="X2" s="49" t="s">
         <v>319</v>
-      </c>
-      <c r="X2" s="49" t="s">
-        <v>320</v>
       </c>
       <c r="Y2" s="49" t="s">
         <v>305</v>

--- a/GRM_Data.xlsx
+++ b/GRM_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ipTime Cloud\Hana Contact Mgr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AD8ABFD-BACF-49B1-9471-2ED4DEE62146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91BB670A-4A41-4A96-95EA-00D6052F9244}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
